--- a/nursing/フォーマット/02_訪問看護記録様式/09_精神科訪問看護計画書（別紙様式3準拠）.xlsx
+++ b/nursing/フォーマット/02_訪問看護記録様式/09_精神科訪問看護計画書（別紙様式3準拠）.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精神科訪看計画書" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精神科訪問看護計画書" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,37 +26,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00163A2B"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -68,21 +68,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -91,35 +91,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,240 +508,312 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>精神科訪問看護計画書（参考様式）　別紙様式3準拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>精神科訪問看護計画書（参考様式・別紙様式3準拠）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>※ 精神疾患を有する利用者への訪問看護は、一般の訪問看護計画書（別紙様式1）の代わりにこの精神科用様式（別紙様式3）を使用します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>利用者氏名</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>（様）</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>生年月日</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日（　歳）</t>
-        </is>
-      </c>
-    </row>
+          <t>精神科訪問看護指示書に基づき、療養上の目標・支援内容を計画</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>訪問看護ステーション名</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>計画作成日</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日</t>
-        </is>
-      </c>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>利用者氏名 / 生年月日</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>主治医氏名・医療機関</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>計画期間</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月〜　　年　月</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>主たる精神疾患</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>精神疾患名（主診断）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>自立支援医療受給</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>あり（受給者証番号：　　　　）/ なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>【現在の病状・精神状態（GAF/GAS等の評価含む）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>例）統合失調症。陽性症状は落ち着いているが、陰性症状（意欲低下・社会的引きこもり）が中心。GAF：50。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>【看護の目標（精神症状・生活・社会参加）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>短期：服薬を自己管理し、週3回の就労継続支援への通所を維持できる。
-長期：地域で安定した生活を送りながら社会参加の場を広げる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>【問題点・訪問看護の内容】</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>①服薬管理：抗精神病薬の自己管理支援・副作用観察（錐体外路症状等）
-②精神状態の観察：幻覚・妄想・自傷他害リスク・希死念慮の確認
-③生活支援：生活リズム・清潔管理・食事管理の指導
-④コミュニケーション支援：傾聴・感情表出の支援
-⑤危機介入計画：悪化時の対応フロー（主治医・家族・行政への連絡順序）
-⑥服薬拒否時の対応：主治医への報告・家族との連携</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>【緊急時対応計画（クライシスプラン）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>①本人サイン（早期警告サイン）：　　　　
-②対応者：本人→訪問看護師→主治医→家族→救急
-③入院先：○○病院（TEL：○○）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>【家族・関係機関との連携】</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>家族：　　（続柄）TEL：○○
-相談支援専門員：○○ TEL：○○
-主治医：○○クリニック TEL：○○</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>【本人・家族の同意】</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>上記計画について説明を受け、同意します。
-本人署名：　　　　　　日付：　　年　月　日
-家族署名：　　　　　　続柄：</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>精神科主治医 / 医療機関</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>指示期間</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>訪問頻度</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>週　　回（　　　　曜）／ 1回　　分</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="8" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>看護・支援の目標（本人の希望を踏まえて）</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>支援内容（症状観察・服薬支援・生活支援・社会資源活用 等）</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>リスク・緊急時対応</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>作成日 / 作成者</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>本人・家族への説明 / 同意</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>□説明済　□同意取得（署名別紙）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>※ ストレングス（本人の強み）に着目し、回復（リカバリー）を支える視点で計画。多職種・相談支援と連携。</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A11:H11"/>
+  <mergeCells count="20">
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C7:H7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="C5:H5"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C4:H4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>